--- a/retrieval_questions.xlsx
+++ b/retrieval_questions.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">

--- a/retrieval_questions.xlsx
+++ b/retrieval_questions.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1423,6 +1423,326 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/retrieval_questions.xlsx
+++ b/retrieval_questions.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1743,6 +1743,102 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
